--- a/experiment/HAT+CNN_2CH_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.09</v>
+        <v>24.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5746</v>
+        <v>0.5749</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.71</v>
+        <v>28.74</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8134</v>
+        <v>0.8137</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.6</v>
+        <v>26.62</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8156</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>30.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8494</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.27</v>
+        <v>26.28</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7129</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.98</v>
+        <v>33.97</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8935</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.35</v>
+        <v>26.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7517</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.08</v>
+        <v>23.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5917</v>
+        <v>0.5924</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.51</v>
+        <v>27.52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7886</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>29.33</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8035</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         <v>24.57</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7405</v>
+        <v>0.7407</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.1</v>
+        <v>28.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7572</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.04</v>
+        <v>30.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8092</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.51</v>
+        <v>29.57</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8344</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.08</v>
+        <v>25.09</v>
       </c>
       <c r="C16" t="n">
-        <v>0.681</v>
+        <v>0.6808999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.89</v>
+        <v>24.91</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7631</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="18">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.87</v>
+        <v>34.88</v>
       </c>
       <c r="C18" t="n">
         <v>0.8956</v>
@@ -676,7 +676,7 @@
         <v>32.94</v>
       </c>
       <c r="C19" t="n">
-        <v>0.894</v>
+        <v>0.8938</v>
       </c>
     </row>
     <row r="20">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.27</v>
+        <v>26.25</v>
       </c>
       <c r="C20" t="n">
         <v>0.7403999999999999</v>
@@ -702,7 +702,7 @@
         <v>26.05</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8032</v>
+        <v>0.8026</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.21</v>
+        <v>22.23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6935</v>
+        <v>0.6942</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.95</v>
+        <v>23.97</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6335</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.86</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5743</v>
+        <v>0.5741000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.61</v>
+        <v>26.59</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7935</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.76</v>
+        <v>27.79</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8246</v>
+        <v>0.8252</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.08</v>
+        <v>27.09</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8408</v>
+        <v>0.8406</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.85</v>
+        <v>27.84</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7399</v>
+        <v>0.7396</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.65</v>
+        <v>29.67</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8048</v>
+        <v>0.8048999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>32.63</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9032</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.88</v>
+        <v>19.89</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5079</v>
+        <v>0.5076000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>29.83</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8179</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.92</v>
+        <v>20.93</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4323</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.24</v>
+        <v>25.25</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6741</v>
+        <v>0.6742</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.45</v>
+        <v>24.42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7582</v>
+        <v>0.7573</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.12</v>
+        <v>35.14</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8949</v>
+        <v>0.8948</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.01</v>
+        <v>27.02</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7429</v>
+        <v>0.7428</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>27.92</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5133</v>
+        <v>0.5132</v>
       </c>
     </row>
     <row r="39">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.52</v>
+        <v>28.55</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7466</v>
+        <v>0.7472</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.3</v>
+        <v>36.25</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9586</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="42">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.91</v>
+        <v>25.92</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7259</v>
+        <v>0.7266</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.76</v>
+        <v>26.75</v>
       </c>
       <c r="C44" t="n">
-        <v>0.762</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.18</v>
+        <v>28.17</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8782</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.81</v>
+        <v>24.79</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6863</v>
+        <v>0.6839</v>
       </c>
     </row>
     <row r="47">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.7</v>
+        <v>34.71</v>
       </c>
       <c r="C47" t="n">
         <v>0.8712</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.82</v>
+        <v>22.84</v>
       </c>
       <c r="C48" t="n">
-        <v>0.627</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6355</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.37</v>
+        <v>27.38</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8773</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.2</v>
+        <v>32.19</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8409</v>
+        <v>0.8408</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         <v>24.87</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6218</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.64</v>
+        <v>22.68</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7083</v>
+        <v>0.7095</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.66</v>
+        <v>32.68</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8474</v>
       </c>
     </row>
     <row r="55">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.52</v>
+        <v>32.54</v>
       </c>
       <c r="C55" t="n">
         <v>0.7998</v>
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.82</v>
+        <v>27.84</v>
       </c>
       <c r="C56" t="n">
         <v>0.7809</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.72</v>
+        <v>25.73</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6983</v>
+        <v>0.6979</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>21.48</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4292</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>27.53</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7302</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.01</v>
+        <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7919</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.3</v>
+        <v>31.29</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7864</v>
+        <v>0.7862</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.76</v>
+        <v>31.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8159</v>
+        <v>0.8156</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         <v>29</v>
       </c>
       <c r="C63" t="n">
-        <v>0.794</v>
+        <v>0.7939000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.59</v>
+        <v>33.58</v>
       </c>
       <c r="C64" t="n">
         <v>0.9524</v>
@@ -1274,7 +1274,7 @@
         <v>24.36</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6737</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.05</v>
+        <v>26.06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6222</v>
+        <v>0.6221</v>
       </c>
     </row>
     <row r="67">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.37</v>
+        <v>28.39</v>
       </c>
       <c r="C67" t="n">
         <v>0.7948</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.98</v>
+        <v>40</v>
       </c>
       <c r="C68" t="n">
         <v>0.9811</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.99</v>
+        <v>21.01</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5805</v>
+        <v>0.5816</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.81</v>
+        <v>22.82</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6533</v>
+        <v>0.6538</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>29.04</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8132</v>
+        <v>0.8138</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.64</v>
+        <v>30.66</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8215</v>
+        <v>0.8217</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.5</v>
+        <v>25.49</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5984</v>
+        <v>0.5979</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.23</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6068</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6968</v>
+        <v>0.6969</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.18</v>
+        <v>24.19</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7018</v>
+        <v>0.7017</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>30.72</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7856</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>23.66</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4801</v>
+        <v>0.4799</v>
       </c>
     </row>
     <row r="79">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.81</v>
+        <v>32.82</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9535</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="81">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.76</v>
+        <v>29.77</v>
       </c>
       <c r="C81" t="n">
         <v>0.8188</v>
@@ -1495,7 +1495,7 @@
         <v>35.83</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9394</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>28.59</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7211</v>
+        <v>0.7207</v>
       </c>
     </row>
     <row r="84">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="C84" t="n">
         <v>0.5335</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.06</v>
+        <v>21.07</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>25.71</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7921</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.04</v>
+        <v>25.06</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6044</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.41</v>
+        <v>27.4</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6967</v>
+        <v>0.6963</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.79</v>
+        <v>30.81</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8153</v>
+        <v>0.8155</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.24</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5602</v>
+        <v>0.5601</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         <v>25.12</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6472</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         <v>29.15</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7151</v>
+        <v>0.7148</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.77</v>
+        <v>26.83</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7608</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31</v>
+        <v>31.03</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8796</v>
+        <v>0.8798</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         <v>26.03</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7181</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.97</v>
+        <v>26</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8014</v>
+        <v>0.8025</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.93</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3205</v>
+        <v>0.3202</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>27.07</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5629</v>
+        <v>0.5624</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.33</v>
+        <v>26.35</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7372</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.09</v>
+        <v>25.11</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7308</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="102">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.6</v>
+        <v>27.61</v>
       </c>
       <c r="C102" t="n">
         <v>0.7382</v>
